--- a/packages/server/templates/sub-growers-template.xlsx
+++ b/packages/server/templates/sub-growers-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\GitHub\stts-full\stts-uganda-new\packages\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7434ED19-AF3F-413B-A40F-C518AAA892F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBE8F78-AE86-4158-B862-2D98863F32A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9570" xr2:uid="{D7BBBDF7-04C3-4EDA-9E1C-882178D0FC21}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t>Source of seed</t>
   </si>
   <si>
-    <t>planting date</t>
-  </si>
-  <si>
     <t>Quantity planted</t>
   </si>
   <si>
@@ -73,6 +70,9 @@
   </si>
   <si>
     <t>Village</t>
+  </si>
+  <si>
+    <t>planting date(DD/MM/YYYY)</t>
   </si>
 </sst>
 </file>
@@ -490,31 +490,31 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
